--- a/sba_application/09_financial_model/Azalea_Hospice_Operations_Dashboard.xlsx
+++ b/sba_application/09_financial_model/Azalea_Hospice_Operations_Dashboard.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Inputs" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Actuals vs Budget" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Staffing Tracker" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Cap &amp; Payroll" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Revenue Model" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Staffing &amp; Payroll" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Operating Budget" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Detailed P&amp;L" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Debt Schedule" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Cash Flow &amp; BS" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Actuals vs Model" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inputs" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actuals vs Budget" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Staffing Tracker" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cap &amp; Payroll" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revenue Model" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Staffing &amp; Payroll" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Operating Budget" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detailed P&amp;L" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt Schedule" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow &amp; BS" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actuals vs Model" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="rhc_tier1">Inputs!$B$5</definedName>
@@ -99,8 +99,8 @@
     <numFmt numFmtId="168" formatCode="0.0000"/>
     <numFmt numFmtId="169" formatCode="#,##0.0;(#,##0.0);&quot;-&quot;"/>
     <numFmt numFmtId="170" formatCode="$#,##0.00;($#,##0.00);&quot;-&quot;"/>
-    <numFmt numFmtId="171" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
-    <numFmt numFmtId="172" formatCode="0.00x;(0.00x);&quot;-&quot;"/>
+    <numFmt numFmtId="171" formatCode="0.00x;(0.00x);&quot;-&quot;"/>
+    <numFmt numFmtId="172" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="173" formatCode="#,##0.00;(#,##0.00);&quot;&quot;"/>
     <numFmt numFmtId="174" formatCode="#,##0.00;(#,##0.00)"/>
   </numFmts>
@@ -326,7 +326,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -408,7 +408,7 @@
     <xf numFmtId="165" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="171" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -460,7 +460,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="171" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="172" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -495,13 +495,22 @@
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="171" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="6" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -581,13 +590,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -605,14 +614,14 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -647,8 +656,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -671,13 +680,13 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -695,14 +704,14 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -737,8 +746,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1821,7 +1830,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -1836,9 +1845,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1858,9 +1867,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -3746,7 +3755,7 @@
         </is>
       </c>
       <c r="B110" s="9" t="n">
-        <v>500000</v>
+        <v>555000</v>
       </c>
     </row>
     <row r="111">
@@ -3776,7 +3785,7 @@
         </is>
       </c>
       <c r="B113" s="9" t="n">
-        <v>250000</v>
+        <v>195000</v>
       </c>
     </row>
     <row r="114">
@@ -3994,11 +4003,11 @@
     <row r="139">
       <c r="A139" s="12" t="inlineStr">
         <is>
-          <t>Opening cash = equity + loan - startup - capex</t>
+          <t>Opening cash = equity + loan - startup - capex - license (paid at close)</t>
         </is>
       </c>
       <c r="B139" s="23">
-        <f>Inputs!$B$113+Inputs!$B$110-Inputs!$B$138-Inputs!$B$117</f>
+        <f>Inputs!$B$113+Inputs!$B$110-Inputs!$B$138-Inputs!$B$117-Inputs!$B$120</f>
         <v/>
       </c>
     </row>
@@ -4017,10 +4026,10 @@
   <mergeCells count="18">
     <mergeCell ref="A2:V2"/>
     <mergeCell ref="A16:V16"/>
+    <mergeCell ref="A35:V35"/>
     <mergeCell ref="A137:V137"/>
+    <mergeCell ref="A90:V90"/>
     <mergeCell ref="A76:V76"/>
-    <mergeCell ref="A90:V90"/>
-    <mergeCell ref="A109:V109"/>
     <mergeCell ref="A85:V85"/>
     <mergeCell ref="A1:V1"/>
     <mergeCell ref="A80:V80"/>
@@ -4030,7 +4039,7 @@
     <mergeCell ref="A27:V27"/>
     <mergeCell ref="A105:V105"/>
     <mergeCell ref="A69:V69"/>
-    <mergeCell ref="A35:V35"/>
+    <mergeCell ref="A109:V109"/>
     <mergeCell ref="A4:V4"/>
     <mergeCell ref="A24:V24"/>
   </mergeCells>
@@ -4083,7 +4092,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Debt Schedule - SBA 7(a) + Hickory license seller note | Combined DSCR shown (target &gt;= 1.25x)</t>
+          <t>Debt Schedule - SBA 7(a) only (seller paid at close) | DSCR shown (target &gt;= 1.25x)</t>
         </is>
       </c>
     </row>
@@ -4686,7 +4695,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>HICKORY LICENSE SELLER NOTE ($300K, 6%, 36 mo)</t>
+          <t>HICKORY LICENSE - PAID AT CLOSE (no seller note; schedule zeroed)</t>
         </is>
       </c>
     </row>
@@ -4696,9 +4705,8 @@
           <t>Beginning balance</t>
         </is>
       </c>
-      <c r="C18" s="33">
-        <f>Inputs!$B$120</f>
-        <v/>
+      <c r="C18" s="33" t="n">
+        <v>0</v>
       </c>
       <c r="D18" s="24">
         <f>C22</f>
@@ -5486,83 +5494,83 @@
           <t>COMBINED DSCR (period)</t>
         </is>
       </c>
-      <c r="C29" s="60">
+      <c r="C29" s="67">
         <f>IF(C27=0,0,C28/C27)</f>
         <v/>
       </c>
-      <c r="D29" s="60">
+      <c r="D29" s="67">
         <f>IF(D27=0,0,D28/D27)</f>
         <v/>
       </c>
-      <c r="E29" s="60">
+      <c r="E29" s="67">
         <f>IF(E27=0,0,E28/E27)</f>
         <v/>
       </c>
-      <c r="F29" s="60">
+      <c r="F29" s="67">
         <f>IF(F27=0,0,F28/F27)</f>
         <v/>
       </c>
-      <c r="G29" s="60">
+      <c r="G29" s="67">
         <f>IF(G27=0,0,G28/G27)</f>
         <v/>
       </c>
-      <c r="H29" s="60">
+      <c r="H29" s="67">
         <f>IF(H27=0,0,H28/H27)</f>
         <v/>
       </c>
-      <c r="I29" s="60">
+      <c r="I29" s="67">
         <f>IF(I27=0,0,I28/I27)</f>
         <v/>
       </c>
-      <c r="J29" s="60">
+      <c r="J29" s="67">
         <f>IF(J27=0,0,J28/J27)</f>
         <v/>
       </c>
-      <c r="K29" s="60">
+      <c r="K29" s="67">
         <f>IF(K27=0,0,K28/K27)</f>
         <v/>
       </c>
-      <c r="L29" s="60">
+      <c r="L29" s="67">
         <f>IF(L27=0,0,L28/L27)</f>
         <v/>
       </c>
-      <c r="M29" s="60">
+      <c r="M29" s="67">
         <f>IF(M27=0,0,M28/M27)</f>
         <v/>
       </c>
-      <c r="N29" s="60">
+      <c r="N29" s="67">
         <f>IF(N27=0,0,N28/N27)</f>
         <v/>
       </c>
-      <c r="O29" s="60">
+      <c r="O29" s="67">
         <f>IF(O27=0,0,O28/O27)</f>
         <v/>
       </c>
-      <c r="P29" s="60">
+      <c r="P29" s="67">
         <f>IF(P27=0,0,P28/P27)</f>
         <v/>
       </c>
-      <c r="Q29" s="60">
+      <c r="Q29" s="67">
         <f>IF(Q27=0,0,Q28/Q27)</f>
         <v/>
       </c>
-      <c r="R29" s="60">
+      <c r="R29" s="67">
         <f>IF(R27=0,0,R28/R27)</f>
         <v/>
       </c>
-      <c r="S29" s="60">
+      <c r="S29" s="67">
         <f>IF(S27=0,0,S28/S27)</f>
         <v/>
       </c>
-      <c r="T29" s="60">
+      <c r="T29" s="67">
         <f>IF(T27=0,0,T28/T27)</f>
         <v/>
       </c>
-      <c r="U29" s="60">
+      <c r="U29" s="67">
         <f>IF(U27=0,0,U28/U27)</f>
         <v/>
       </c>
-      <c r="V29" s="60">
+      <c r="V29" s="67">
         <f>IF(V27=0,0,V28/V27)</f>
         <v/>
       </c>
@@ -7925,9 +7933,8 @@
           <t>Hickory license note balance</t>
         </is>
       </c>
-      <c r="B34" s="33">
-        <f>Inputs!$B$120</f>
-        <v/>
+      <c r="B34" s="33" t="n">
+        <v>0</v>
       </c>
       <c r="C34" s="33">
         <f>'Debt Schedule'!C22</f>
@@ -8912,7 +8919,7 @@
       <c r="F8" s="26" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="29">
+      <c r="A9" s="65">
         <f>MIN('Debt Schedule'!C29:N29)</f>
         <v/>
       </c>
@@ -10477,83 +10484,83 @@
           <t>Patient-days</t>
         </is>
       </c>
-      <c r="C12" s="47">
+      <c r="C12" s="66">
         <f>C10*C11</f>
         <v/>
       </c>
-      <c r="D12" s="47">
+      <c r="D12" s="66">
         <f>D10*D11</f>
         <v/>
       </c>
-      <c r="E12" s="47">
+      <c r="E12" s="66">
         <f>E10*E11</f>
         <v/>
       </c>
-      <c r="F12" s="47">
+      <c r="F12" s="66">
         <f>F10*F11</f>
         <v/>
       </c>
-      <c r="G12" s="47">
+      <c r="G12" s="66">
         <f>G10*G11</f>
         <v/>
       </c>
-      <c r="H12" s="47">
+      <c r="H12" s="66">
         <f>H10*H11</f>
         <v/>
       </c>
-      <c r="I12" s="47">
+      <c r="I12" s="66">
         <f>I10*I11</f>
         <v/>
       </c>
-      <c r="J12" s="47">
+      <c r="J12" s="66">
         <f>J10*J11</f>
         <v/>
       </c>
-      <c r="K12" s="47">
+      <c r="K12" s="66">
         <f>K10*K11</f>
         <v/>
       </c>
-      <c r="L12" s="47">
+      <c r="L12" s="66">
         <f>L10*L11</f>
         <v/>
       </c>
-      <c r="M12" s="47">
+      <c r="M12" s="66">
         <f>M10*M11</f>
         <v/>
       </c>
-      <c r="N12" s="47">
+      <c r="N12" s="66">
         <f>N10*N11</f>
         <v/>
       </c>
-      <c r="O12" s="47">
+      <c r="O12" s="66">
         <f>O10*O11</f>
         <v/>
       </c>
-      <c r="P12" s="47">
+      <c r="P12" s="66">
         <f>P10*P11</f>
         <v/>
       </c>
-      <c r="Q12" s="47">
+      <c r="Q12" s="66">
         <f>Q10*Q11</f>
         <v/>
       </c>
-      <c r="R12" s="47">
+      <c r="R12" s="66">
         <f>R10*R11</f>
         <v/>
       </c>
-      <c r="S12" s="47">
+      <c r="S12" s="66">
         <f>S10*S11</f>
         <v/>
       </c>
-      <c r="T12" s="47">
+      <c r="T12" s="66">
         <f>T10*T11</f>
         <v/>
       </c>
-      <c r="U12" s="47">
+      <c r="U12" s="66">
         <f>U10*U11</f>
         <v/>
       </c>
-      <c r="V12" s="47">
+      <c r="V12" s="66">
         <f>V10*V11</f>
         <v/>
       </c>

--- a/sba_application/09_financial_model/Azalea_Hospice_Operations_Dashboard.xlsx
+++ b/sba_application/09_financial_model/Azalea_Hospice_Operations_Dashboard.xlsx
@@ -99,8 +99,8 @@
     <numFmt numFmtId="168" formatCode="0.0000"/>
     <numFmt numFmtId="169" formatCode="#,##0.0;(#,##0.0);&quot;-&quot;"/>
     <numFmt numFmtId="170" formatCode="$#,##0.00;($#,##0.00);&quot;-&quot;"/>
-    <numFmt numFmtId="171" formatCode="0.00x;(0.00x);&quot;-&quot;"/>
-    <numFmt numFmtId="172" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
+    <numFmt numFmtId="171" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
+    <numFmt numFmtId="172" formatCode="0.00x;(0.00x);&quot;-&quot;"/>
     <numFmt numFmtId="173" formatCode="#,##0.00;(#,##0.00);&quot;&quot;"/>
     <numFmt numFmtId="174" formatCode="#,##0.00;(#,##0.00)"/>
   </numFmts>
@@ -326,7 +326,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -408,7 +408,7 @@
     <xf numFmtId="165" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="172" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -460,7 +460,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="172" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="171" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -495,22 +495,13 @@
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="172" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="6" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1457,7 +1448,7 @@
     </comment>
     <comment ref="B110" authorId="0" shapeId="0">
       <text>
-        <t>Sized to fund ramp-period operating need + startup costs. FLAG / CONFIRM: go-forward assumption, not in Paloma actuals.</t>
+        <t>Sized to pay the seller in full at close + fund startup costs and working-capital reserve. FLAG / CONFIRM: go-forward assumption, not in Paloma actuals.</t>
       </text>
     </comment>
     <comment ref="B111" authorId="0" shapeId="0">
@@ -1472,7 +1463,7 @@
     </comment>
     <comment ref="B113" authorId="0" shapeId="0">
       <text>
-        <t>FLAG / CONFIRM: go-forward assumption, not in Paloma actuals.</t>
+        <t>Cash capital contribution by James Bullard (19.5% passive member). FLAG / CONFIRM: go-forward assumption, not in Paloma actuals.</t>
       </text>
     </comment>
     <comment ref="B114" authorId="0" shapeId="0">
@@ -4026,10 +4017,10 @@
   <mergeCells count="18">
     <mergeCell ref="A2:V2"/>
     <mergeCell ref="A16:V16"/>
-    <mergeCell ref="A35:V35"/>
     <mergeCell ref="A137:V137"/>
+    <mergeCell ref="A76:V76"/>
     <mergeCell ref="A90:V90"/>
-    <mergeCell ref="A76:V76"/>
+    <mergeCell ref="A109:V109"/>
     <mergeCell ref="A85:V85"/>
     <mergeCell ref="A1:V1"/>
     <mergeCell ref="A80:V80"/>
@@ -4039,7 +4030,7 @@
     <mergeCell ref="A27:V27"/>
     <mergeCell ref="A105:V105"/>
     <mergeCell ref="A69:V69"/>
-    <mergeCell ref="A109:V109"/>
+    <mergeCell ref="A35:V35"/>
     <mergeCell ref="A4:V4"/>
     <mergeCell ref="A24:V24"/>
   </mergeCells>
@@ -4121,7 +4112,7 @@
         </is>
       </c>
       <c r="B6" s="24">
-        <f>PMT(Inputs!$B$121/12,Inputs!$B$122,-Inputs!$B$120)</f>
+        <f>0</f>
         <v/>
       </c>
     </row>
@@ -4705,8 +4696,9 @@
           <t>Beginning balance</t>
         </is>
       </c>
-      <c r="C18" s="33" t="n">
-        <v>0</v>
+      <c r="C18" s="33">
+        <f>0</f>
+        <v/>
       </c>
       <c r="D18" s="24">
         <f>C22</f>
@@ -5136,7 +5128,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>COMBINED DEBT SERVICE &amp; COVERAGE</t>
+          <t>DEBT SERVICE &amp; COVERAGE (SBA only)</t>
         </is>
       </c>
     </row>
@@ -5317,7 +5309,7 @@
     <row r="27">
       <c r="A27" s="31" t="inlineStr">
         <is>
-          <t>TOTAL DEBT SERVICE (P+I, combined)</t>
+          <t>TOTAL DEBT SERVICE (P+I)</t>
         </is>
       </c>
       <c r="C27" s="23">
@@ -5491,86 +5483,86 @@
     <row r="29">
       <c r="A29" s="31" t="inlineStr">
         <is>
-          <t>COMBINED DSCR (period)</t>
-        </is>
-      </c>
-      <c r="C29" s="67">
+          <t>DSCR (period)</t>
+        </is>
+      </c>
+      <c r="C29" s="60">
         <f>IF(C27=0,0,C28/C27)</f>
         <v/>
       </c>
-      <c r="D29" s="67">
+      <c r="D29" s="60">
         <f>IF(D27=0,0,D28/D27)</f>
         <v/>
       </c>
-      <c r="E29" s="67">
+      <c r="E29" s="60">
         <f>IF(E27=0,0,E28/E27)</f>
         <v/>
       </c>
-      <c r="F29" s="67">
+      <c r="F29" s="60">
         <f>IF(F27=0,0,F28/F27)</f>
         <v/>
       </c>
-      <c r="G29" s="67">
+      <c r="G29" s="60">
         <f>IF(G27=0,0,G28/G27)</f>
         <v/>
       </c>
-      <c r="H29" s="67">
+      <c r="H29" s="60">
         <f>IF(H27=0,0,H28/H27)</f>
         <v/>
       </c>
-      <c r="I29" s="67">
+      <c r="I29" s="60">
         <f>IF(I27=0,0,I28/I27)</f>
         <v/>
       </c>
-      <c r="J29" s="67">
+      <c r="J29" s="60">
         <f>IF(J27=0,0,J28/J27)</f>
         <v/>
       </c>
-      <c r="K29" s="67">
+      <c r="K29" s="60">
         <f>IF(K27=0,0,K28/K27)</f>
         <v/>
       </c>
-      <c r="L29" s="67">
+      <c r="L29" s="60">
         <f>IF(L27=0,0,L28/L27)</f>
         <v/>
       </c>
-      <c r="M29" s="67">
+      <c r="M29" s="60">
         <f>IF(M27=0,0,M28/M27)</f>
         <v/>
       </c>
-      <c r="N29" s="67">
+      <c r="N29" s="60">
         <f>IF(N27=0,0,N28/N27)</f>
         <v/>
       </c>
-      <c r="O29" s="67">
+      <c r="O29" s="60">
         <f>IF(O27=0,0,O28/O27)</f>
         <v/>
       </c>
-      <c r="P29" s="67">
+      <c r="P29" s="60">
         <f>IF(P27=0,0,P28/P27)</f>
         <v/>
       </c>
-      <c r="Q29" s="67">
+      <c r="Q29" s="60">
         <f>IF(Q27=0,0,Q28/Q27)</f>
         <v/>
       </c>
-      <c r="R29" s="67">
+      <c r="R29" s="60">
         <f>IF(R27=0,0,R28/R27)</f>
         <v/>
       </c>
-      <c r="S29" s="67">
+      <c r="S29" s="60">
         <f>IF(S27=0,0,S28/S27)</f>
         <v/>
       </c>
-      <c r="T29" s="67">
+      <c r="T29" s="60">
         <f>IF(T27=0,0,T28/T27)</f>
         <v/>
       </c>
-      <c r="U29" s="67">
+      <c r="U29" s="60">
         <f>IF(U27=0,0,U28/U27)</f>
         <v/>
       </c>
-      <c r="V29" s="67">
+      <c r="V29" s="60">
         <f>IF(V27=0,0,V28/V27)</f>
         <v/>
       </c>
@@ -7933,8 +7925,9 @@
           <t>Hickory license note balance</t>
         </is>
       </c>
-      <c r="B34" s="33" t="n">
-        <v>0</v>
+      <c r="B34" s="33">
+        <f>0</f>
+        <v/>
       </c>
       <c r="C34" s="33">
         <f>'Debt Schedule'!C22</f>
@@ -8919,7 +8912,7 @@
       <c r="F8" s="26" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="65">
+      <c r="A9" s="29">
         <f>MIN('Debt Schedule'!C29:N29)</f>
         <v/>
       </c>
@@ -10484,83 +10477,83 @@
           <t>Patient-days</t>
         </is>
       </c>
-      <c r="C12" s="66">
+      <c r="C12" s="47">
         <f>C10*C11</f>
         <v/>
       </c>
-      <c r="D12" s="66">
+      <c r="D12" s="47">
         <f>D10*D11</f>
         <v/>
       </c>
-      <c r="E12" s="66">
+      <c r="E12" s="47">
         <f>E10*E11</f>
         <v/>
       </c>
-      <c r="F12" s="66">
+      <c r="F12" s="47">
         <f>F10*F11</f>
         <v/>
       </c>
-      <c r="G12" s="66">
+      <c r="G12" s="47">
         <f>G10*G11</f>
         <v/>
       </c>
-      <c r="H12" s="66">
+      <c r="H12" s="47">
         <f>H10*H11</f>
         <v/>
       </c>
-      <c r="I12" s="66">
+      <c r="I12" s="47">
         <f>I10*I11</f>
         <v/>
       </c>
-      <c r="J12" s="66">
+      <c r="J12" s="47">
         <f>J10*J11</f>
         <v/>
       </c>
-      <c r="K12" s="66">
+      <c r="K12" s="47">
         <f>K10*K11</f>
         <v/>
       </c>
-      <c r="L12" s="66">
+      <c r="L12" s="47">
         <f>L10*L11</f>
         <v/>
       </c>
-      <c r="M12" s="66">
+      <c r="M12" s="47">
         <f>M10*M11</f>
         <v/>
       </c>
-      <c r="N12" s="66">
+      <c r="N12" s="47">
         <f>N10*N11</f>
         <v/>
       </c>
-      <c r="O12" s="66">
+      <c r="O12" s="47">
         <f>O10*O11</f>
         <v/>
       </c>
-      <c r="P12" s="66">
+      <c r="P12" s="47">
         <f>P10*P11</f>
         <v/>
       </c>
-      <c r="Q12" s="66">
+      <c r="Q12" s="47">
         <f>Q10*Q11</f>
         <v/>
       </c>
-      <c r="R12" s="66">
+      <c r="R12" s="47">
         <f>R10*R11</f>
         <v/>
       </c>
-      <c r="S12" s="66">
+      <c r="S12" s="47">
         <f>S10*S11</f>
         <v/>
       </c>
-      <c r="T12" s="66">
+      <c r="T12" s="47">
         <f>T10*T11</f>
         <v/>
       </c>
-      <c r="U12" s="66">
+      <c r="U12" s="47">
         <f>U10*U11</f>
         <v/>
       </c>
-      <c r="V12" s="66">
+      <c r="V12" s="47">
         <f>V10*V11</f>
         <v/>
       </c>
